--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2021.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2021.xlsx
@@ -2041,7 +2041,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:47</t>
+    <t xml:space="preserve">2026-09-07 12:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2021.xlsx
@@ -2041,7 +2041,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:52</t>
+    <t xml:space="preserve">2026-09-08 10:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
